--- a/documentation/Jira_Backlog_English_to_Hindi_Translator.xlsx
+++ b/documentation/Jira_Backlog_English_to_Hindi_Translator.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoj Prajapati\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\college\GitHubINV\aitranslator_webapp\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6D6DE68-B27D-4AA9-86F2-D0A121A20E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF050E6-7CB7-4D25-8DF6-8545FAE1811C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="61">
   <si>
     <t>Issue ID</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>document-setup</t>
+  </si>
+  <si>
+    <t>Done</t>
   </si>
 </sst>
 </file>
@@ -605,7 +608,7 @@
         <v>59</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">

--- a/documentation/Jira_Backlog_English_to_Hindi_Translator.xlsx
+++ b/documentation/Jira_Backlog_English_to_Hindi_Translator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\college\GitHubINV\aitranslator_webapp\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF050E6-7CB7-4D25-8DF6-8545FAE1811C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E191004-F2DB-4BF0-AE70-92AFD82E0CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -637,7 +637,7 @@
         <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
